--- a/output/pdf_financials_xlsx/SHRC.xlsx
+++ b/output/pdf_financials_xlsx/SHRC.xlsx
@@ -1888,13 +1888,13 @@
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>0</v>
+        <v>0.002002</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.097446</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.012437</v>
       </c>
     </row>
     <row r="92">
@@ -1904,13 +1904,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.882983</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>5.133412</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.872236</v>
       </c>
     </row>
     <row r="93">
@@ -3242,7 +3242,11 @@
           <t>Reserves 11,13</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -3302,7 +3306,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -3521,7 +3529,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>4.882983</v>
       </c>
@@ -3579,7 +3591,11 @@
           <t>Currency translation reserve</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.002002</v>
       </c>

--- a/output/pdf_financials_xlsx/SHRC.xlsx
+++ b/output/pdf_financials_xlsx/SHRC.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.015934</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004878</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.003335</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.90349</v>
+        <v>-3.919424</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.776407</v>
+        <v>-3.781285</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.53594</v>
+        <v>-3.539275</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.74291</v>
+        <v>-3.758844</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.612192</v>
+        <v>-3.61707</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.328082</v>
+        <v>-3.331417</v>
       </c>
     </row>
     <row r="30">
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-235.0982562236898</v>
+        <v>-236.0990966432212</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-166.7426939700239</v>
+        <v>-166.9678677318798</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-109.4296579947115</v>
+        <v>-109.5393151213725</v>
       </c>
     </row>
     <row r="31">
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.242268</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.818259</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.262513</v>
       </c>
     </row>
     <row r="35">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.242268</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.818259</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.262513</v>
       </c>
     </row>
     <row r="37">
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.454187</v>
+        <v>0.211919</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.78714</v>
+        <v>0.968881</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.565983</v>
+        <v>0.30347</v>
       </c>
     </row>
     <row r="49">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">

--- a/output/pdf_financials_xlsx/SHRC.xlsx
+++ b/output/pdf_financials_xlsx/SHRC.xlsx
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.100638</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.159245</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.179441</v>
       </c>
     </row>
     <row r="71">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.100638</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.159245</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.179441</v>
       </c>
     </row>
     <row r="72">
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.100638</v>
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.319245</v>
+        <v>0.16</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.339441</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="76">
@@ -1705,20 +1705,14 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.03717131871419548</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>6.803306703122997</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>-0.06200442777702719</v>
       </c>
     </row>
     <row r="81">
@@ -3060,7 +3054,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>0.100638</v>
       </c>
@@ -3992,7 +3990,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
